--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:27:44+00:00</t>
+    <t>2026-04-30T07:27:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T07:27:20+00:00</t>
+    <t>2026-04-30T08:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:16:21+00:00</t>
+    <t>2026-04-30T08:30:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:30:02+00:00</t>
+    <t>2026-04-30T08:50:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:50:01+00:00</t>
+    <t>2026-04-30T09:39:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:39:49+00:00</t>
+    <t>2026-04-30T09:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:58:38+00:00</t>
+    <t>2026-04-30T12:46:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:46:52+00:00</t>
+    <t>2026-04-30T13:16:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:16:04+00:00</t>
+    <t>2026-04-30T13:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:33:12+00:00</t>
+    <t>2026-04-30T13:47:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T13:47:19+00:00</t>
+    <t>2026-04-30T14:01:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
+++ b/feature/fix-specialty-profiling/ig/StructureDefinition-sas-cpts-bundle-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T14:01:16+00:00</t>
+    <t>2026-05-05T11:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
